--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264075209315189</v>
+        <v>1.248946477192746</v>
       </c>
       <c r="C3" t="n">
-        <v>4.619885657507604</v>
+        <v>4.575019787423525</v>
       </c>
       <c r="D3" t="n">
-        <v>6.17647433440112</v>
+        <v>6.06947365211526</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06043520122391</v>
+        <v>11.89343991673153</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.398742185790236</v>
+        <v>1.369239886367968</v>
       </c>
       <c r="C4" t="n">
-        <v>5.098248231904641</v>
+        <v>4.960776942571053</v>
       </c>
       <c r="D4" t="n">
-        <v>6.584732821048905</v>
+        <v>6.327302311161481</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08172323874378</v>
+        <v>12.6573191401005</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.577219379919552</v>
+        <v>1.537778381995944</v>
       </c>
       <c r="C5" t="n">
-        <v>5.698982468737947</v>
+        <v>5.422233336092297</v>
       </c>
       <c r="D5" t="n">
-        <v>6.993901399430845</v>
+        <v>6.573845293646044</v>
       </c>
       <c r="E5" t="n">
-        <v>14.27010324808834</v>
+        <v>13.53385701173429</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.780741233856588</v>
+        <v>1.740463041038813</v>
       </c>
       <c r="C6" t="n">
-        <v>6.459048297011092</v>
+        <v>5.981531235418867</v>
       </c>
       <c r="D6" t="n">
-        <v>7.41321081606444</v>
+        <v>6.982811441698898</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65300034693212</v>
+        <v>14.70480571815658</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.019410493823655</v>
+        <v>1.971039085361879</v>
       </c>
       <c r="C7" t="n">
-        <v>7.369415998813261</v>
+        <v>6.626971281838715</v>
       </c>
       <c r="D7" t="n">
-        <v>7.839878709814529</v>
+        <v>7.437801083069899</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22870520245144</v>
+        <v>16.03581145027049</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.239085881079631</v>
+        <v>1.20959612962647</v>
       </c>
       <c r="C8" t="n">
-        <v>5.064281545332609</v>
+        <v>4.238163363370188</v>
       </c>
       <c r="D8" t="n">
-        <v>6.151228913939422</v>
+        <v>5.818353172175612</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45459634035166</v>
+        <v>11.26611266517227</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.546284163419588</v>
+        <v>1.529407901098171</v>
       </c>
       <c r="C9" t="n">
-        <v>6.231757138351147</v>
+        <v>5.024701104641357</v>
       </c>
       <c r="D9" t="n">
-        <v>6.734248393126324</v>
+        <v>6.435140789983307</v>
       </c>
       <c r="E9" t="n">
-        <v>14.51228969489706</v>
+        <v>12.98924979572283</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.864787685728964</v>
+        <v>1.885987559564591</v>
       </c>
       <c r="C10" t="n">
-        <v>7.610677865079214</v>
+        <v>5.927894158770219</v>
       </c>
       <c r="D10" t="n">
-        <v>7.405553640706226</v>
+        <v>7.059375809432455</v>
       </c>
       <c r="E10" t="n">
-        <v>16.8810191915144</v>
+        <v>14.87325752776727</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.19315831827661</v>
+        <v>2.265968638779869</v>
       </c>
       <c r="C11" t="n">
-        <v>9.099716845962813</v>
+        <v>6.928432879563015</v>
       </c>
       <c r="D11" t="n">
-        <v>7.95034284047484</v>
+        <v>7.844988864491254</v>
       </c>
       <c r="E11" t="n">
-        <v>19.24321800471427</v>
+        <v>17.03939038283414</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.51097835736757</v>
+        <v>2.650301499182932</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69838574659603</v>
+        <v>8.021996526552071</v>
       </c>
       <c r="D12" t="n">
-        <v>8.459509379192854</v>
+        <v>8.566309468543034</v>
       </c>
       <c r="E12" t="n">
-        <v>21.66887348315645</v>
+        <v>19.23860749427804</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.82109195855044</v>
+        <v>3.049842881156078</v>
       </c>
       <c r="C13" t="n">
-        <v>12.38542379411473</v>
+        <v>9.187113133813231</v>
       </c>
       <c r="D13" t="n">
-        <v>9.144479999341199</v>
+        <v>9.166477555496769</v>
       </c>
       <c r="E13" t="n">
-        <v>24.35099575200637</v>
+        <v>21.40343357046608</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.625430586536232</v>
+        <v>1.765928500490993</v>
       </c>
       <c r="C14" t="n">
-        <v>8.684353659703477</v>
+        <v>6.58164642674766</v>
       </c>
       <c r="D14" t="n">
-        <v>6.888216782352812</v>
+        <v>7.03133596267791</v>
       </c>
       <c r="E14" t="n">
-        <v>17.19800102859252</v>
+        <v>15.37891088991656</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.654009262206856</v>
+        <v>1.842485186468159</v>
       </c>
       <c r="C15" t="n">
-        <v>9.523355247752802</v>
+        <v>7.004976036818884</v>
       </c>
       <c r="D15" t="n">
-        <v>6.971635884782661</v>
+        <v>7.18610848825242</v>
       </c>
       <c r="E15" t="n">
-        <v>18.14900039474232</v>
+        <v>16.03356971153946</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.906819113527453</v>
+        <v>2.186774288870473</v>
       </c>
       <c r="C16" t="n">
-        <v>11.35908601001574</v>
+        <v>8.21686503789523</v>
       </c>
       <c r="D16" t="n">
-        <v>7.520049969851973</v>
+        <v>7.879605249055325</v>
       </c>
       <c r="E16" t="n">
-        <v>20.78595509339517</v>
+        <v>18.28324457582103</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.524290938044725</v>
+        <v>1.789539532778128</v>
       </c>
       <c r="C17" t="n">
-        <v>10.59979251807422</v>
+        <v>7.609281018690965</v>
       </c>
       <c r="D17" t="n">
-        <v>7.038326006332149</v>
+        <v>7.450277160511153</v>
       </c>
       <c r="E17" t="n">
-        <v>19.16240946245109</v>
+        <v>16.84909771198025</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.724773636728967</v>
+        <v>2.089679440920464</v>
       </c>
       <c r="C18" t="n">
-        <v>12.42782637833586</v>
+        <v>8.867547781315933</v>
       </c>
       <c r="D18" t="n">
-        <v>7.513806054452964</v>
+        <v>8.079155287420532</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66640606951779</v>
+        <v>19.03638250965693</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.716222614224977</v>
+        <v>2.143655929699953</v>
       </c>
       <c r="C19" t="n">
-        <v>13.33233017321253</v>
+        <v>9.499518413493689</v>
       </c>
       <c r="D19" t="n">
-        <v>7.62648123846937</v>
+        <v>8.304859084626873</v>
       </c>
       <c r="E19" t="n">
-        <v>22.67503402590688</v>
+        <v>19.94803342782052</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.89006068021596</v>
+        <v>2.443403138760589</v>
       </c>
       <c r="C20" t="n">
-        <v>15.36374288788595</v>
+        <v>10.94387545345864</v>
       </c>
       <c r="D20" t="n">
-        <v>8.11884734710323</v>
+        <v>8.906032291322408</v>
       </c>
       <c r="E20" t="n">
-        <v>25.37265091520514</v>
+        <v>22.29331088354164</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.114479993860979</v>
+        <v>1.48914437023269</v>
       </c>
       <c r="C21" t="n">
-        <v>11.30913468682366</v>
+        <v>8.124217507045461</v>
       </c>
       <c r="D21" t="n">
-        <v>6.786105203634101</v>
+        <v>7.511312415284177</v>
       </c>
       <c r="E21" t="n">
-        <v>19.20971988431874</v>
+        <v>17.12467429256233</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248946477192746</v>
+        <v>1.255808893645431</v>
       </c>
       <c r="C3" t="n">
-        <v>4.575019787423525</v>
+        <v>4.715115184819545</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06947365211526</v>
+        <v>6.065684105976866</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89343991673153</v>
+        <v>12.03660818444184</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.369239886367968</v>
+        <v>1.381290789948566</v>
       </c>
       <c r="C4" t="n">
-        <v>4.960776942571053</v>
+        <v>5.347604047660768</v>
       </c>
       <c r="D4" t="n">
-        <v>6.327302311161481</v>
+        <v>6.326101685646813</v>
       </c>
       <c r="E4" t="n">
-        <v>12.6573191401005</v>
+        <v>13.05499652325615</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.537778381995944</v>
+        <v>1.551477855672966</v>
       </c>
       <c r="C5" t="n">
-        <v>5.422233336092297</v>
+        <v>6.221817337659672</v>
       </c>
       <c r="D5" t="n">
-        <v>6.573845293646044</v>
+        <v>6.653865310490195</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53385701173429</v>
+        <v>14.42716050382283</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.740463041038813</v>
+        <v>1.749943363335128</v>
       </c>
       <c r="C6" t="n">
-        <v>5.981531235418867</v>
+        <v>7.258151021342425</v>
       </c>
       <c r="D6" t="n">
-        <v>6.982811441698898</v>
+        <v>6.996561887860806</v>
       </c>
       <c r="E6" t="n">
-        <v>14.70480571815658</v>
+        <v>16.00465627253836</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.971039085361879</v>
+        <v>1.978154320779781</v>
       </c>
       <c r="C7" t="n">
-        <v>6.626971281838715</v>
+        <v>8.44025315315236</v>
       </c>
       <c r="D7" t="n">
-        <v>7.437801083069899</v>
+        <v>7.327042116709982</v>
       </c>
       <c r="E7" t="n">
-        <v>16.03581145027049</v>
+        <v>17.74544959064212</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.20959612962647</v>
+        <v>1.223795227389173</v>
       </c>
       <c r="C8" t="n">
-        <v>4.238163363370188</v>
+        <v>5.974231598286143</v>
       </c>
       <c r="D8" t="n">
-        <v>5.818353172175612</v>
+        <v>5.540241339914986</v>
       </c>
       <c r="E8" t="n">
-        <v>11.26611266517227</v>
+        <v>12.7382681655903</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.529407901098171</v>
+        <v>1.538702760161506</v>
       </c>
       <c r="C9" t="n">
-        <v>5.024701104641357</v>
+        <v>7.338881954799708</v>
       </c>
       <c r="D9" t="n">
-        <v>6.435140789983307</v>
+        <v>5.964541733545288</v>
       </c>
       <c r="E9" t="n">
-        <v>12.98924979572283</v>
+        <v>14.8421264485065</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.885987559564591</v>
+        <v>1.866993928942419</v>
       </c>
       <c r="C10" t="n">
-        <v>5.927894158770219</v>
+        <v>8.878051991849082</v>
       </c>
       <c r="D10" t="n">
-        <v>7.059375809432455</v>
+        <v>6.463393786836837</v>
       </c>
       <c r="E10" t="n">
-        <v>14.87325752776727</v>
+        <v>17.20843970762834</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.265968638779869</v>
+        <v>2.200009269994068</v>
       </c>
       <c r="C11" t="n">
-        <v>6.928432879563015</v>
+        <v>10.53616066138012</v>
       </c>
       <c r="D11" t="n">
-        <v>7.844988864491254</v>
+        <v>6.910277675337583</v>
       </c>
       <c r="E11" t="n">
-        <v>17.03939038283414</v>
+        <v>19.64644760671177</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.650301499182932</v>
+        <v>2.522970054414097</v>
       </c>
       <c r="C12" t="n">
-        <v>8.021996526552071</v>
+        <v>12.28222436559214</v>
       </c>
       <c r="D12" t="n">
-        <v>8.566309468543034</v>
+        <v>7.322419954239431</v>
       </c>
       <c r="E12" t="n">
-        <v>19.23860749427804</v>
+        <v>22.12761437424567</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.049842881156078</v>
+        <v>2.822925965403221</v>
       </c>
       <c r="C13" t="n">
-        <v>9.187113133813231</v>
+        <v>14.06176723200463</v>
       </c>
       <c r="D13" t="n">
-        <v>9.166477555496769</v>
+        <v>7.734847503352018</v>
       </c>
       <c r="E13" t="n">
-        <v>21.40343357046608</v>
+        <v>24.61954070075987</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.765928500490993</v>
+        <v>1.607032634558646</v>
       </c>
       <c r="C14" t="n">
-        <v>6.58164642674766</v>
+        <v>9.90688480589386</v>
       </c>
       <c r="D14" t="n">
-        <v>7.03133596267791</v>
+        <v>5.878577625828349</v>
       </c>
       <c r="E14" t="n">
-        <v>15.37891088991656</v>
+        <v>17.39249506628085</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.842485186468159</v>
+        <v>1.645556414473291</v>
       </c>
       <c r="C15" t="n">
-        <v>7.004976036818884</v>
+        <v>10.71789676689511</v>
       </c>
       <c r="D15" t="n">
-        <v>7.18610848825242</v>
+        <v>5.835017480190918</v>
       </c>
       <c r="E15" t="n">
-        <v>16.03356971153946</v>
+        <v>18.19847066155932</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.186774288870473</v>
+        <v>1.894537449747325</v>
       </c>
       <c r="C16" t="n">
-        <v>8.21686503789523</v>
+        <v>12.64182774290758</v>
       </c>
       <c r="D16" t="n">
-        <v>7.879605249055325</v>
+        <v>6.258621979619331</v>
       </c>
       <c r="E16" t="n">
-        <v>18.28324457582103</v>
+        <v>20.79498717227424</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.789539532778128</v>
+        <v>1.512480513162636</v>
       </c>
       <c r="C17" t="n">
-        <v>7.609281018690965</v>
+        <v>11.57153621321475</v>
       </c>
       <c r="D17" t="n">
-        <v>7.450277160511153</v>
+        <v>5.780314498110286</v>
       </c>
       <c r="E17" t="n">
-        <v>16.84909771198025</v>
+        <v>18.86433122448768</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.089679440920464</v>
+        <v>1.71150040776755</v>
       </c>
       <c r="C18" t="n">
-        <v>8.867547781315933</v>
+        <v>13.46099802733112</v>
       </c>
       <c r="D18" t="n">
-        <v>8.079155287420532</v>
+        <v>6.17468255090623</v>
       </c>
       <c r="E18" t="n">
-        <v>19.03638250965693</v>
+        <v>21.3471809860049</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.143655929699953</v>
+        <v>1.7051779525522</v>
       </c>
       <c r="C19" t="n">
-        <v>9.499518413493689</v>
+        <v>14.3353818026415</v>
       </c>
       <c r="D19" t="n">
-        <v>8.304859084626873</v>
+        <v>6.23801509530719</v>
       </c>
       <c r="E19" t="n">
-        <v>19.94803342782052</v>
+        <v>22.27857485050089</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.443403138760589</v>
+        <v>1.88210852381156</v>
       </c>
       <c r="C20" t="n">
-        <v>10.94387545345864</v>
+        <v>16.32039712081221</v>
       </c>
       <c r="D20" t="n">
-        <v>8.906032291322408</v>
+        <v>6.627435139673731</v>
       </c>
       <c r="E20" t="n">
-        <v>22.29331088354164</v>
+        <v>24.8299407842975</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.48914437023269</v>
+        <v>1.106459115117283</v>
       </c>
       <c r="C21" t="n">
-        <v>8.124217507045461</v>
+        <v>11.88044312835601</v>
       </c>
       <c r="D21" t="n">
-        <v>7.511312415284177</v>
+        <v>5.514201965397145</v>
       </c>
       <c r="E21" t="n">
-        <v>17.12467429256233</v>
+        <v>18.50110420887044</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255808893645431</v>
+        <v>2.593138820495842</v>
       </c>
       <c r="C3" t="n">
-        <v>4.715115184819545</v>
+        <v>7.678039797252919</v>
       </c>
       <c r="D3" t="n">
-        <v>6.065684105976866</v>
+        <v>8.191445394889703</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03660818444184</v>
+        <v>18.46262401263846</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.381290789948566</v>
+        <v>1.082920791389611</v>
       </c>
       <c r="C4" t="n">
-        <v>5.347604047660768</v>
+        <v>4.424580651050467</v>
       </c>
       <c r="D4" t="n">
-        <v>6.326101685646813</v>
+        <v>5.827163764304954</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05499652325615</v>
+        <v>11.33466520674503</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.551477855672966</v>
+        <v>1.18556942325669</v>
       </c>
       <c r="C5" t="n">
-        <v>6.221817337659672</v>
+        <v>4.985718573327222</v>
       </c>
       <c r="D5" t="n">
-        <v>6.653865310490195</v>
+        <v>6.155875279225072</v>
       </c>
       <c r="E5" t="n">
-        <v>14.42716050382283</v>
+        <v>12.32716327580899</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.749943363335128</v>
+        <v>1.309688891419036</v>
       </c>
       <c r="C6" t="n">
-        <v>7.258151021342425</v>
+        <v>5.695797143436721</v>
       </c>
       <c r="D6" t="n">
-        <v>6.996561887860806</v>
+        <v>6.547772555799733</v>
       </c>
       <c r="E6" t="n">
-        <v>16.00465627253836</v>
+        <v>13.55325859065549</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.978154320779781</v>
+        <v>1.44072005231569</v>
       </c>
       <c r="C7" t="n">
-        <v>8.44025315315236</v>
+        <v>6.540883609779686</v>
       </c>
       <c r="D7" t="n">
-        <v>7.327042116709982</v>
+        <v>6.974048998896779</v>
       </c>
       <c r="E7" t="n">
-        <v>17.74544959064212</v>
+        <v>14.95565266099216</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.223795227389173</v>
+        <v>1.580393440830007</v>
       </c>
       <c r="C8" t="n">
-        <v>5.974231598286143</v>
+        <v>7.524562417624207</v>
       </c>
       <c r="D8" t="n">
-        <v>5.540241339914986</v>
+        <v>7.428039480381856</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7382681655903</v>
+        <v>16.53299533883607</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.538702760161506</v>
+        <v>1.721078771420766</v>
       </c>
       <c r="C9" t="n">
-        <v>7.338881954799708</v>
+        <v>8.633241254344686</v>
       </c>
       <c r="D9" t="n">
-        <v>5.964541733545288</v>
+        <v>7.936589095031334</v>
       </c>
       <c r="E9" t="n">
-        <v>14.8421264485065</v>
+        <v>18.29090912079678</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.866993928942419</v>
+        <v>1.071283094874119</v>
       </c>
       <c r="C10" t="n">
-        <v>8.878051991849082</v>
+        <v>6.448884684702363</v>
       </c>
       <c r="D10" t="n">
-        <v>6.463393786836837</v>
+        <v>6.26792894785559</v>
       </c>
       <c r="E10" t="n">
-        <v>17.20843970762834</v>
+        <v>13.78809672743207</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.200009269994068</v>
+        <v>1.008392336940069</v>
       </c>
       <c r="C11" t="n">
-        <v>10.53616066138012</v>
+        <v>6.779007167732395</v>
       </c>
       <c r="D11" t="n">
-        <v>6.910277675337583</v>
+        <v>6.179532384565208</v>
       </c>
       <c r="E11" t="n">
-        <v>19.64644760671177</v>
+        <v>13.96693188923767</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.522970054414097</v>
+        <v>1.097103059495811</v>
       </c>
       <c r="C12" t="n">
-        <v>12.28222436559214</v>
+        <v>7.973322884902725</v>
       </c>
       <c r="D12" t="n">
-        <v>7.322419954239431</v>
+        <v>6.697119591721169</v>
       </c>
       <c r="E12" t="n">
-        <v>22.12761437424567</v>
+        <v>15.76754553611971</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.822925965403221</v>
+        <v>0.8747470219609506</v>
       </c>
       <c r="C13" t="n">
-        <v>14.06176723200463</v>
+        <v>7.571650629187185</v>
       </c>
       <c r="D13" t="n">
-        <v>7.734847503352018</v>
+        <v>6.205774500699725</v>
       </c>
       <c r="E13" t="n">
-        <v>24.61954070075987</v>
+        <v>14.65217215184786</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.607032634558646</v>
+        <v>0.9585980933806706</v>
       </c>
       <c r="C14" t="n">
-        <v>9.90688480589386</v>
+        <v>8.841570737061563</v>
       </c>
       <c r="D14" t="n">
-        <v>5.878577625828349</v>
+        <v>6.67222246994147</v>
       </c>
       <c r="E14" t="n">
-        <v>17.39249506628085</v>
+        <v>16.47239130038371</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.645556414473291</v>
+        <v>0.9363418729253955</v>
       </c>
       <c r="C15" t="n">
-        <v>10.71789676689511</v>
+        <v>9.526123776278776</v>
       </c>
       <c r="D15" t="n">
-        <v>5.835017480190918</v>
+        <v>6.802068421305153</v>
       </c>
       <c r="E15" t="n">
-        <v>18.19847066155932</v>
+        <v>17.26453407050932</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.894537449747325</v>
+        <v>1.033348363582023</v>
       </c>
       <c r="C16" t="n">
-        <v>12.64182774290758</v>
+        <v>11.11614272312283</v>
       </c>
       <c r="D16" t="n">
-        <v>6.258621979619331</v>
+        <v>7.324780351477282</v>
       </c>
       <c r="E16" t="n">
-        <v>20.79498717227424</v>
+        <v>19.47427143818213</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.512480513162636</v>
+        <v>0.6273956878759667</v>
       </c>
       <c r="C17" t="n">
-        <v>11.57153621321475</v>
+        <v>8.360013670651458</v>
       </c>
       <c r="D17" t="n">
-        <v>5.780314498110286</v>
+        <v>6.157158354385424</v>
       </c>
       <c r="E17" t="n">
-        <v>18.86433122448768</v>
+        <v>15.14456771291285</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.71150040776755</v>
+        <v>0.5010054884312323</v>
       </c>
       <c r="C18" t="n">
-        <v>13.46099802733112</v>
+        <v>7.36701513771398</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17468255090623</v>
+        <v>5.704484305434262</v>
       </c>
       <c r="E18" t="n">
-        <v>21.3471809860049</v>
+        <v>13.57250493157947</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.7051779525522</v>
+        <v>0.5949292912965246</v>
       </c>
       <c r="C19" t="n">
-        <v>14.3353818026415</v>
+        <v>9.118227240118314</v>
       </c>
       <c r="D19" t="n">
-        <v>6.23801509530719</v>
+        <v>6.373437373630996</v>
       </c>
       <c r="E19" t="n">
-        <v>22.27857485050089</v>
+        <v>16.08659390504583</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.88210852381156</v>
+        <v>0.6863889074241575</v>
       </c>
       <c r="C20" t="n">
-        <v>16.32039712081221</v>
+        <v>10.9448375662088</v>
       </c>
       <c r="D20" t="n">
-        <v>6.627435139673731</v>
+        <v>6.981639893888937</v>
       </c>
       <c r="E20" t="n">
-        <v>24.8299407842975</v>
+        <v>18.6128663675219</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.106459115117283</v>
+        <v>0.7693956758182253</v>
       </c>
       <c r="C21" t="n">
-        <v>11.88044312835601</v>
+        <v>12.79106321143014</v>
       </c>
       <c r="D21" t="n">
-        <v>5.514201965397145</v>
+        <v>7.532459260833654</v>
       </c>
       <c r="E21" t="n">
-        <v>18.50110420887044</v>
+        <v>21.09291814808202</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.593138820495842</v>
+        <v>2.546625289075436</v>
       </c>
       <c r="C3" t="n">
-        <v>7.678039797252919</v>
+        <v>7.566936083086675</v>
       </c>
       <c r="D3" t="n">
-        <v>8.191445394889703</v>
+        <v>8.114562203387189</v>
       </c>
       <c r="E3" t="n">
-        <v>18.46262401263846</v>
+        <v>18.2281235755493</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.082920791389611</v>
+        <v>1.016130426597547</v>
       </c>
       <c r="C4" t="n">
-        <v>4.424580651050467</v>
+        <v>4.259081392870201</v>
       </c>
       <c r="D4" t="n">
-        <v>5.827163764304954</v>
+        <v>5.688032627001788</v>
       </c>
       <c r="E4" t="n">
-        <v>11.33466520674503</v>
+        <v>10.96324444646954</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.18556942325669</v>
+        <v>1.068133387936838</v>
       </c>
       <c r="C5" t="n">
-        <v>4.985718573327222</v>
+        <v>4.655089405304403</v>
       </c>
       <c r="D5" t="n">
-        <v>6.155875279225072</v>
+        <v>5.961926846735518</v>
       </c>
       <c r="E5" t="n">
-        <v>12.32716327580899</v>
+        <v>11.68514963997676</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.309688891419036</v>
+        <v>1.140799860211348</v>
       </c>
       <c r="C6" t="n">
-        <v>5.695797143436721</v>
+        <v>5.180108747239192</v>
       </c>
       <c r="D6" t="n">
-        <v>6.547772555799733</v>
+        <v>6.26907939824487</v>
       </c>
       <c r="E6" t="n">
-        <v>13.55325859065549</v>
+        <v>12.58998800569541</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.44072005231569</v>
+        <v>1.214845278996412</v>
       </c>
       <c r="C7" t="n">
-        <v>6.540883609779686</v>
+        <v>5.830597426647862</v>
       </c>
       <c r="D7" t="n">
-        <v>6.974048998896779</v>
+        <v>6.67748488110229</v>
       </c>
       <c r="E7" t="n">
-        <v>14.95565266099216</v>
+        <v>13.72292758674656</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.580393440830007</v>
+        <v>1.287596422252205</v>
       </c>
       <c r="C8" t="n">
-        <v>7.524562417624207</v>
+        <v>6.570326515065174</v>
       </c>
       <c r="D8" t="n">
-        <v>7.428039480381856</v>
+        <v>7.075038451125031</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53299533883607</v>
+        <v>14.93296138844241</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.721078771420766</v>
+        <v>1.363230498427792</v>
       </c>
       <c r="C9" t="n">
-        <v>8.633241254344686</v>
+        <v>7.455880987434088</v>
       </c>
       <c r="D9" t="n">
-        <v>7.936589095031334</v>
+        <v>7.507920512966659</v>
       </c>
       <c r="E9" t="n">
-        <v>18.29090912079678</v>
+        <v>16.32703199882854</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.071283094874119</v>
+        <v>0.87792788452271</v>
       </c>
       <c r="C10" t="n">
-        <v>6.448884684702363</v>
+        <v>5.746110408094325</v>
       </c>
       <c r="D10" t="n">
-        <v>6.26792894785559</v>
+        <v>5.950608454888936</v>
       </c>
       <c r="E10" t="n">
-        <v>13.78809672743207</v>
+        <v>12.57464674750597</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.008392336940069</v>
+        <v>0.7961581182359931</v>
       </c>
       <c r="C11" t="n">
-        <v>6.779007167732395</v>
+        <v>5.974514011487346</v>
       </c>
       <c r="D11" t="n">
-        <v>6.179532384565208</v>
+        <v>5.852040985382557</v>
       </c>
       <c r="E11" t="n">
-        <v>13.96693188923767</v>
+        <v>12.6227131151059</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.097103059495811</v>
+        <v>0.8465512278949821</v>
       </c>
       <c r="C12" t="n">
-        <v>7.973322884902725</v>
+        <v>6.99641519683785</v>
       </c>
       <c r="D12" t="n">
-        <v>6.697119591721169</v>
+        <v>6.284942635570189</v>
       </c>
       <c r="E12" t="n">
-        <v>15.76754553611971</v>
+        <v>14.12790906030302</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8747470219609506</v>
+        <v>0.6609910943152926</v>
       </c>
       <c r="C13" t="n">
-        <v>7.571650629187185</v>
+        <v>6.642750403859981</v>
       </c>
       <c r="D13" t="n">
-        <v>6.205774500699725</v>
+        <v>5.794441847574396</v>
       </c>
       <c r="E13" t="n">
-        <v>14.65217215184786</v>
+        <v>13.09818334574967</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9585980933806706</v>
+        <v>0.7115118311758333</v>
       </c>
       <c r="C14" t="n">
-        <v>8.841570737061563</v>
+        <v>7.749828020030941</v>
       </c>
       <c r="D14" t="n">
-        <v>6.67222246994147</v>
+        <v>6.185638855285622</v>
       </c>
       <c r="E14" t="n">
-        <v>16.47239130038371</v>
+        <v>14.6469787064924</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9363418729253955</v>
+        <v>0.6864576297634548</v>
       </c>
       <c r="C15" t="n">
-        <v>9.526123776278776</v>
+        <v>8.339809302898058</v>
       </c>
       <c r="D15" t="n">
-        <v>6.802068421305153</v>
+        <v>6.286042192998943</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26453407050932</v>
+        <v>15.31230912566046</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.033348363582023</v>
+        <v>0.7495938246235673</v>
       </c>
       <c r="C16" t="n">
-        <v>11.11614272312283</v>
+        <v>9.733086009811046</v>
       </c>
       <c r="D16" t="n">
-        <v>7.324780351477282</v>
+        <v>6.7168919904847</v>
       </c>
       <c r="E16" t="n">
-        <v>19.47427143818213</v>
+        <v>17.19957182491931</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6273956878759667</v>
+        <v>0.4537147015176634</v>
       </c>
       <c r="C17" t="n">
-        <v>8.360013670651458</v>
+        <v>7.324986518495173</v>
       </c>
       <c r="D17" t="n">
-        <v>6.157158354385424</v>
+        <v>5.612789069857611</v>
       </c>
       <c r="E17" t="n">
-        <v>15.14456771291285</v>
+        <v>13.39149028987045</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5010054884312323</v>
+        <v>0.3462722327648926</v>
       </c>
       <c r="C18" t="n">
-        <v>7.36701513771398</v>
+        <v>6.423643951226177</v>
       </c>
       <c r="D18" t="n">
-        <v>5.704484305434262</v>
+        <v>5.124212507362142</v>
       </c>
       <c r="E18" t="n">
-        <v>13.57250493157947</v>
+        <v>11.89412869135321</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5949292912965246</v>
+        <v>0.4027030908049992</v>
       </c>
       <c r="C19" t="n">
-        <v>9.118227240118314</v>
+        <v>7.925492136751823</v>
       </c>
       <c r="D19" t="n">
-        <v>6.373437373630996</v>
+        <v>5.61712839471038</v>
       </c>
       <c r="E19" t="n">
-        <v>16.08659390504583</v>
+        <v>13.9453236222672</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6863889074241575</v>
+        <v>0.4576515098116932</v>
       </c>
       <c r="C20" t="n">
-        <v>10.9448375662088</v>
+        <v>9.557412075613122</v>
       </c>
       <c r="D20" t="n">
-        <v>6.981639893888937</v>
+        <v>6.127745193166189</v>
       </c>
       <c r="E20" t="n">
-        <v>18.6128663675219</v>
+        <v>16.142808778591</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7693956758182253</v>
+        <v>0.509369978871415</v>
       </c>
       <c r="C21" t="n">
-        <v>12.79106321143014</v>
+        <v>11.30946848104311</v>
       </c>
       <c r="D21" t="n">
-        <v>7.532459260833654</v>
+        <v>6.60308779660841</v>
       </c>
       <c r="E21" t="n">
-        <v>21.09291814808202</v>
+        <v>18.42192625652294</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.075208479759865</v>
+        <v>2.066461107715026</v>
       </c>
       <c r="C3" t="n">
-        <v>6.036472109102364</v>
+        <v>6.107688087568426</v>
       </c>
       <c r="D3" t="n">
-        <v>6.247106079048516</v>
+        <v>6.126596548352221</v>
       </c>
       <c r="E3" t="n">
-        <v>14.35878666791075</v>
+        <v>14.30074574363567</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.203100753192097</v>
+        <v>2.225445330940754</v>
       </c>
       <c r="C4" t="n">
-        <v>6.397234937981938</v>
+        <v>6.552665234518294</v>
       </c>
       <c r="D4" t="n">
-        <v>6.486789963563331</v>
+        <v>6.423339609437861</v>
       </c>
       <c r="E4" t="n">
-        <v>15.08712565473737</v>
+        <v>15.20145017489691</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.344691051288047</v>
+        <v>2.411789306241233</v>
       </c>
       <c r="C5" t="n">
-        <v>6.826182226297047</v>
+        <v>7.148012516815815</v>
       </c>
       <c r="D5" t="n">
-        <v>6.731343316691214</v>
+        <v>6.725482282896859</v>
       </c>
       <c r="E5" t="n">
-        <v>15.90221659427631</v>
+        <v>16.28528410595391</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.49219644639244</v>
+        <v>2.589981142571603</v>
       </c>
       <c r="C6" t="n">
-        <v>7.246969262092605</v>
+        <v>7.66650289059927</v>
       </c>
       <c r="D6" t="n">
-        <v>6.977006044724893</v>
+        <v>7.020368192017463</v>
       </c>
       <c r="E6" t="n">
-        <v>16.71617175320994</v>
+        <v>17.27685222518834</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.641763827466592</v>
+        <v>2.76799575257718</v>
       </c>
       <c r="C7" t="n">
-        <v>7.668570015821567</v>
+        <v>8.22555025225965</v>
       </c>
       <c r="D7" t="n">
-        <v>7.212988740394698</v>
+        <v>7.313371206232122</v>
       </c>
       <c r="E7" t="n">
-        <v>17.52332258368286</v>
+        <v>18.30691721106895</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.785423666133099</v>
+        <v>2.952252220481015</v>
       </c>
       <c r="C8" t="n">
-        <v>8.088301634425742</v>
+        <v>8.755377718615383</v>
       </c>
       <c r="D8" t="n">
-        <v>7.447135567857562</v>
+        <v>7.609711530815757</v>
       </c>
       <c r="E8" t="n">
-        <v>18.3208608684164</v>
+        <v>19.31734146991215</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.924950048521607</v>
+        <v>3.131893826286896</v>
       </c>
       <c r="C9" t="n">
-        <v>8.498679098863608</v>
+        <v>9.291515166822796</v>
       </c>
       <c r="D9" t="n">
-        <v>7.680575536973368</v>
+        <v>7.892612662010122</v>
       </c>
       <c r="E9" t="n">
-        <v>19.10420468435859</v>
+        <v>20.31602165511982</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.071658229614981</v>
+        <v>3.30570063866002</v>
       </c>
       <c r="C10" t="n">
-        <v>8.905989981361763</v>
+        <v>9.825134180162367</v>
       </c>
       <c r="D10" t="n">
-        <v>7.920455771029033</v>
+        <v>8.166560955587187</v>
       </c>
       <c r="E10" t="n">
-        <v>19.89810398200578</v>
+        <v>21.29739577440957</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.211852158042192</v>
+        <v>3.481208169147408</v>
       </c>
       <c r="C11" t="n">
-        <v>9.320564183214943</v>
+        <v>10.33805933398676</v>
       </c>
       <c r="D11" t="n">
-        <v>8.152678372991573</v>
+        <v>8.438010433026703</v>
       </c>
       <c r="E11" t="n">
-        <v>20.68509471424871</v>
+        <v>22.25727793616087</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.345089575912252</v>
+        <v>3.64968014967882</v>
       </c>
       <c r="C12" t="n">
-        <v>9.714370409853572</v>
+        <v>10.86042821657384</v>
       </c>
       <c r="D12" t="n">
-        <v>8.371460848882975</v>
+        <v>8.702756334415536</v>
       </c>
       <c r="E12" t="n">
-        <v>21.4309208346488</v>
+        <v>23.2128647006682</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.48262093938189</v>
+        <v>3.815377585410751</v>
       </c>
       <c r="C13" t="n">
-        <v>10.10499067754723</v>
+        <v>11.35092252132109</v>
       </c>
       <c r="D13" t="n">
-        <v>8.601661050574767</v>
+        <v>8.967620997201777</v>
       </c>
       <c r="E13" t="n">
-        <v>22.18927266750389</v>
+        <v>24.13392110393362</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3.619146042600355</v>
+        <v>3.981555538979574</v>
       </c>
       <c r="C14" t="n">
-        <v>10.48425989693034</v>
+        <v>11.84359255962254</v>
       </c>
       <c r="D14" t="n">
-        <v>8.823005887974256</v>
+        <v>9.227575799761876</v>
       </c>
       <c r="E14" t="n">
-        <v>22.92641182750495</v>
+        <v>25.05272389836399</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.751852525153705</v>
+        <v>4.137243778408778</v>
       </c>
       <c r="C15" t="n">
-        <v>10.84834119597746</v>
+        <v>12.31110957533212</v>
       </c>
       <c r="D15" t="n">
-        <v>9.038627136257983</v>
+        <v>9.491713248390933</v>
       </c>
       <c r="E15" t="n">
-        <v>23.63882085738915</v>
+        <v>25.94006660213184</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3.874931121739261</v>
+        <v>4.296424429387683</v>
       </c>
       <c r="C16" t="n">
-        <v>11.20959773794106</v>
+        <v>12.76157765734568</v>
       </c>
       <c r="D16" t="n">
-        <v>9.255593378896526</v>
+        <v>9.742845593046367</v>
       </c>
       <c r="E16" t="n">
-        <v>24.34012223857685</v>
+        <v>26.80084767977974</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3.997433187328425</v>
+        <v>4.447399207158943</v>
       </c>
       <c r="C17" t="n">
-        <v>11.55961868679902</v>
+        <v>13.19927944291253</v>
       </c>
       <c r="D17" t="n">
-        <v>9.457990485604048</v>
+        <v>9.984850355066408</v>
       </c>
       <c r="E17" t="n">
-        <v>25.01504235973149</v>
+        <v>27.63152900513788</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.112623646558611</v>
+        <v>4.601184465703652</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8914810441827</v>
+        <v>13.62217160430935</v>
       </c>
       <c r="D18" t="n">
-        <v>9.659062232910838</v>
+        <v>10.23041227846843</v>
       </c>
       <c r="E18" t="n">
-        <v>25.66316692365215</v>
+        <v>28.45376834848143</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.221218923104063</v>
+        <v>4.736646594755819</v>
       </c>
       <c r="C19" t="n">
-        <v>12.22899907854554</v>
+        <v>14.036032578936</v>
       </c>
       <c r="D19" t="n">
-        <v>9.860624854069751</v>
+        <v>10.45807939134152</v>
       </c>
       <c r="E19" t="n">
-        <v>26.31084285571936</v>
+        <v>29.23075856503334</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.33473460745294</v>
+        <v>4.877524739200531</v>
       </c>
       <c r="C20" t="n">
-        <v>12.55069645056503</v>
+        <v>14.43699107145801</v>
       </c>
       <c r="D20" t="n">
-        <v>10.06741037301525</v>
+        <v>10.69002065641468</v>
       </c>
       <c r="E20" t="n">
-        <v>26.95284143103323</v>
+        <v>30.00453646707322</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.441575981299168</v>
+        <v>5.007526371636684</v>
       </c>
       <c r="C21" t="n">
-        <v>12.85799487146381</v>
+        <v>14.81696736499216</v>
       </c>
       <c r="D21" t="n">
-        <v>10.26316104776503</v>
+        <v>10.9074786693669</v>
       </c>
       <c r="E21" t="n">
-        <v>27.562731900528</v>
+        <v>30.73197240599574</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.066461107715026</v>
+        <v>2.454772320396871</v>
       </c>
       <c r="C3" t="n">
-        <v>6.107688087568426</v>
+        <v>7.724683513815532</v>
       </c>
       <c r="D3" t="n">
-        <v>6.126596548352221</v>
+        <v>7.854727762229712</v>
       </c>
       <c r="E3" t="n">
-        <v>14.30074574363567</v>
+        <v>18.03418359644212</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.225445330940754</v>
+        <v>2.438723971683934</v>
       </c>
       <c r="C4" t="n">
-        <v>6.552665234518294</v>
+        <v>8.16366648343819</v>
       </c>
       <c r="D4" t="n">
-        <v>6.423339609437861</v>
+        <v>7.959439260167439</v>
       </c>
       <c r="E4" t="n">
-        <v>15.20145017489691</v>
+        <v>18.56182971528956</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.411789306241233</v>
+        <v>2.412419592986753</v>
       </c>
       <c r="C5" t="n">
-        <v>7.148012516815815</v>
+        <v>8.626621028583406</v>
       </c>
       <c r="D5" t="n">
-        <v>6.725482282896859</v>
+        <v>8.061983779706493</v>
       </c>
       <c r="E5" t="n">
-        <v>16.28528410595391</v>
+        <v>19.10102440127665</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.589981142571603</v>
+        <v>2.378903019690497</v>
       </c>
       <c r="C6" t="n">
-        <v>7.66650289059927</v>
+        <v>9.094570045495914</v>
       </c>
       <c r="D6" t="n">
-        <v>7.020368192017463</v>
+        <v>8.166728227074218</v>
       </c>
       <c r="E6" t="n">
-        <v>17.27685222518834</v>
+        <v>19.64020129226063</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.76799575257718</v>
+        <v>2.361805581531228</v>
       </c>
       <c r="C7" t="n">
-        <v>8.22555025225965</v>
+        <v>9.562151428974035</v>
       </c>
       <c r="D7" t="n">
-        <v>7.313371206232122</v>
+        <v>8.252207544872761</v>
       </c>
       <c r="E7" t="n">
-        <v>18.30691721106895</v>
+        <v>20.17616455537802</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.952252220481015</v>
+        <v>2.335619814204586</v>
       </c>
       <c r="C8" t="n">
-        <v>8.755377718615383</v>
+        <v>10.05271482894103</v>
       </c>
       <c r="D8" t="n">
-        <v>7.609711530815757</v>
+        <v>8.337762164399896</v>
       </c>
       <c r="E8" t="n">
-        <v>19.31734146991215</v>
+        <v>20.72609680754552</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.131893826286896</v>
+        <v>2.316035610421166</v>
       </c>
       <c r="C9" t="n">
-        <v>9.291515166822796</v>
+        <v>10.5445329488738</v>
       </c>
       <c r="D9" t="n">
-        <v>7.892612662010122</v>
+        <v>8.413948335587024</v>
       </c>
       <c r="E9" t="n">
-        <v>20.31602165511982</v>
+        <v>21.27451689488199</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.30570063866002</v>
+        <v>2.282571051337436</v>
       </c>
       <c r="C10" t="n">
-        <v>9.825134180162367</v>
+        <v>11.04478220264458</v>
       </c>
       <c r="D10" t="n">
-        <v>8.166560955587187</v>
+        <v>8.48401223326236</v>
       </c>
       <c r="E10" t="n">
-        <v>21.29739577440957</v>
+        <v>21.81136548724437</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.481208169147408</v>
+        <v>2.255029779249211</v>
       </c>
       <c r="C11" t="n">
-        <v>10.33805933398676</v>
+        <v>11.54876782478959</v>
       </c>
       <c r="D11" t="n">
-        <v>8.438010433026703</v>
+        <v>8.548311456743722</v>
       </c>
       <c r="E11" t="n">
-        <v>22.25727793616087</v>
+        <v>22.35210906078252</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.64968014967882</v>
+        <v>2.226561907650802</v>
       </c>
       <c r="C12" t="n">
-        <v>10.86042821657384</v>
+        <v>12.04136349429338</v>
       </c>
       <c r="D12" t="n">
-        <v>8.702756334415536</v>
+        <v>8.60826818546969</v>
       </c>
       <c r="E12" t="n">
-        <v>23.2128647006682</v>
+        <v>22.87619358741388</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.815377585410751</v>
+        <v>2.200227741880843</v>
       </c>
       <c r="C13" t="n">
-        <v>11.35092252132109</v>
+        <v>12.52754420415943</v>
       </c>
       <c r="D13" t="n">
-        <v>8.967620997201777</v>
+        <v>8.662017431059711</v>
       </c>
       <c r="E13" t="n">
-        <v>24.13392110393362</v>
+        <v>23.38978937709998</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3.981555538979574</v>
+        <v>2.175027644400325</v>
       </c>
       <c r="C14" t="n">
-        <v>11.84359255962254</v>
+        <v>13.02486627300089</v>
       </c>
       <c r="D14" t="n">
-        <v>9.227575799761876</v>
+        <v>8.713224712975107</v>
       </c>
       <c r="E14" t="n">
-        <v>25.05272389836399</v>
+        <v>23.91311863037632</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.137243778408778</v>
+        <v>2.145437393526562</v>
       </c>
       <c r="C15" t="n">
-        <v>12.31110957533212</v>
+        <v>13.51893265875224</v>
       </c>
       <c r="D15" t="n">
-        <v>9.491713248390933</v>
+        <v>8.754285489489272</v>
       </c>
       <c r="E15" t="n">
-        <v>25.94006660213184</v>
+        <v>24.41865554176808</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.296424429387683</v>
+        <v>2.121310421064158</v>
       </c>
       <c r="C16" t="n">
-        <v>12.76157765734568</v>
+        <v>14.00935138953808</v>
       </c>
       <c r="D16" t="n">
-        <v>9.742845593046367</v>
+        <v>8.804178914408016</v>
       </c>
       <c r="E16" t="n">
-        <v>26.80084767977974</v>
+        <v>24.93484072501025</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.447399207158943</v>
+        <v>2.091900913308455</v>
       </c>
       <c r="C17" t="n">
-        <v>13.19927944291253</v>
+        <v>14.50460493062339</v>
       </c>
       <c r="D17" t="n">
-        <v>9.984850355066408</v>
+        <v>8.853245005113349</v>
       </c>
       <c r="E17" t="n">
-        <v>27.63152900513788</v>
+        <v>25.44975084904519</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.601184465703652</v>
+        <v>2.068445089667567</v>
       </c>
       <c r="C18" t="n">
-        <v>13.62217160430935</v>
+        <v>14.99248715272302</v>
       </c>
       <c r="D18" t="n">
-        <v>10.23041227846843</v>
+        <v>8.891047120764227</v>
       </c>
       <c r="E18" t="n">
-        <v>28.45376834848143</v>
+        <v>25.95197936315481</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.736646594755819</v>
+        <v>2.032628333574301</v>
       </c>
       <c r="C19" t="n">
-        <v>14.036032578936</v>
+        <v>15.4920820951334</v>
       </c>
       <c r="D19" t="n">
-        <v>10.45807939134152</v>
+        <v>8.920210043011606</v>
       </c>
       <c r="E19" t="n">
-        <v>29.23075856503334</v>
+        <v>26.44492047171931</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.877524739200531</v>
+        <v>2.003679427316052</v>
       </c>
       <c r="C20" t="n">
-        <v>14.43699107145801</v>
+        <v>15.98183449481387</v>
       </c>
       <c r="D20" t="n">
-        <v>10.69002065641468</v>
+        <v>8.94229123649297</v>
       </c>
       <c r="E20" t="n">
-        <v>30.00453646707322</v>
+        <v>26.9278051586229</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>5.007526371636684</v>
+        <v>1.982748020731403</v>
       </c>
       <c r="C21" t="n">
-        <v>14.81696736499216</v>
+        <v>16.47721708468845</v>
       </c>
       <c r="D21" t="n">
-        <v>10.9074786693669</v>
+        <v>8.964324779842842</v>
       </c>
       <c r="E21" t="n">
-        <v>30.73197240599574</v>
+        <v>27.4242898852627</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.454772320396871</v>
+        <v>2.445290276272423</v>
       </c>
       <c r="C3" t="n">
-        <v>7.724683513815532</v>
+        <v>7.676302650519829</v>
       </c>
       <c r="D3" t="n">
-        <v>7.854727762229712</v>
+        <v>7.843535838401297</v>
       </c>
       <c r="E3" t="n">
-        <v>18.03418359644212</v>
+        <v>17.96512876519355</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.438723971683934</v>
+        <v>2.413134251246658</v>
       </c>
       <c r="C4" t="n">
-        <v>8.16366648343819</v>
+        <v>8.075242440420171</v>
       </c>
       <c r="D4" t="n">
-        <v>7.959439260167439</v>
+        <v>7.93805488642495</v>
       </c>
       <c r="E4" t="n">
-        <v>18.56182971528956</v>
+        <v>18.42643157809178</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.412419592986753</v>
+        <v>2.381111852937855</v>
       </c>
       <c r="C5" t="n">
-        <v>8.626621028583406</v>
+        <v>8.481976758288409</v>
       </c>
       <c r="D5" t="n">
-        <v>8.061983779706493</v>
+        <v>8.029313182768718</v>
       </c>
       <c r="E5" t="n">
-        <v>19.10102440127665</v>
+        <v>18.89240179399498</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.378903019690497</v>
+        <v>2.345964089736273</v>
       </c>
       <c r="C6" t="n">
-        <v>9.094570045495914</v>
+        <v>8.893356793775554</v>
       </c>
       <c r="D6" t="n">
-        <v>8.166728227074218</v>
+        <v>8.109155896207723</v>
       </c>
       <c r="E6" t="n">
-        <v>19.64020129226063</v>
+        <v>19.34847677971955</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.361805581531228</v>
+        <v>2.30853208850806</v>
       </c>
       <c r="C7" t="n">
-        <v>9.562151428974035</v>
+        <v>9.310146309339702</v>
       </c>
       <c r="D7" t="n">
-        <v>8.252207544872761</v>
+        <v>8.18283703348756</v>
       </c>
       <c r="E7" t="n">
-        <v>20.17616455537802</v>
+        <v>19.80151543133532</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.335619814204586</v>
+        <v>2.269328368059262</v>
       </c>
       <c r="C8" t="n">
-        <v>10.05271482894103</v>
+        <v>9.722573070078763</v>
       </c>
       <c r="D8" t="n">
-        <v>8.337762164399896</v>
+        <v>8.24863784906244</v>
       </c>
       <c r="E8" t="n">
-        <v>20.72609680754552</v>
+        <v>20.24053928720046</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.316035610421166</v>
+        <v>2.234618776873122</v>
       </c>
       <c r="C9" t="n">
-        <v>10.5445329488738</v>
+        <v>10.1330253399421</v>
       </c>
       <c r="D9" t="n">
-        <v>8.413948335587024</v>
+        <v>8.309669043159994</v>
       </c>
       <c r="E9" t="n">
-        <v>21.27451689488199</v>
+        <v>20.67731315997521</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.282571051337436</v>
+        <v>2.198281367066394</v>
       </c>
       <c r="C10" t="n">
-        <v>11.04478220264458</v>
+        <v>10.54847820669292</v>
       </c>
       <c r="D10" t="n">
-        <v>8.48401223326236</v>
+        <v>8.370428001281567</v>
       </c>
       <c r="E10" t="n">
-        <v>21.81136548724437</v>
+        <v>21.11718757504088</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.255029779249211</v>
+        <v>2.15652167054319</v>
       </c>
       <c r="C11" t="n">
-        <v>11.54876782478959</v>
+        <v>10.96205453526991</v>
       </c>
       <c r="D11" t="n">
-        <v>8.548311456743722</v>
+        <v>8.427303803920244</v>
       </c>
       <c r="E11" t="n">
-        <v>22.35210906078252</v>
+        <v>21.54588000973335</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.226561907650802</v>
+        <v>2.121316005823477</v>
       </c>
       <c r="C12" t="n">
-        <v>12.04136349429338</v>
+        <v>11.37894032098361</v>
       </c>
       <c r="D12" t="n">
-        <v>8.60826818546969</v>
+        <v>8.47514812551451</v>
       </c>
       <c r="E12" t="n">
-        <v>22.87619358741388</v>
+        <v>21.97540445232159</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.200227741880843</v>
+        <v>2.08419367590241</v>
       </c>
       <c r="C13" t="n">
-        <v>12.52754420415943</v>
+        <v>11.78639144008061</v>
       </c>
       <c r="D13" t="n">
-        <v>8.662017431059711</v>
+        <v>8.517997337962113</v>
       </c>
       <c r="E13" t="n">
-        <v>23.38978937709998</v>
+        <v>22.38858245394513</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.175027644400325</v>
+        <v>2.045018594862198</v>
       </c>
       <c r="C14" t="n">
-        <v>13.02486627300089</v>
+        <v>12.1948537917535</v>
       </c>
       <c r="D14" t="n">
-        <v>8.713224712975107</v>
+        <v>8.563326012630002</v>
       </c>
       <c r="E14" t="n">
-        <v>23.91311863037632</v>
+        <v>22.80319839924569</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.145437393526562</v>
+        <v>2.002275255018093</v>
       </c>
       <c r="C15" t="n">
-        <v>13.51893265875224</v>
+        <v>12.6001915291353</v>
       </c>
       <c r="D15" t="n">
-        <v>8.754285489489272</v>
+        <v>8.599880691815356</v>
       </c>
       <c r="E15" t="n">
-        <v>24.41865554176808</v>
+        <v>23.20234747596875</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.121310421064158</v>
+        <v>1.964601065294169</v>
       </c>
       <c r="C16" t="n">
-        <v>14.00935138953808</v>
+        <v>12.9961380394988</v>
       </c>
       <c r="D16" t="n">
-        <v>8.804178914408016</v>
+        <v>8.62949801615469</v>
       </c>
       <c r="E16" t="n">
-        <v>24.93484072501025</v>
+        <v>23.59023712094766</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.091900913308455</v>
+        <v>1.932325130041396</v>
       </c>
       <c r="C17" t="n">
-        <v>14.50460493062339</v>
+        <v>13.39270713381045</v>
       </c>
       <c r="D17" t="n">
-        <v>8.853245005113349</v>
+        <v>8.657841668529098</v>
       </c>
       <c r="E17" t="n">
-        <v>25.44975084904519</v>
+        <v>23.98287393238094</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.068445089667567</v>
+        <v>1.890579684098039</v>
       </c>
       <c r="C18" t="n">
-        <v>14.99248715272302</v>
+        <v>13.78387250357022</v>
       </c>
       <c r="D18" t="n">
-        <v>8.891047120764227</v>
+        <v>8.684314086764971</v>
       </c>
       <c r="E18" t="n">
-        <v>25.95197936315481</v>
+        <v>24.35876627443323</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.032628333574301</v>
+        <v>1.848491129095178</v>
       </c>
       <c r="C19" t="n">
-        <v>15.4920820951334</v>
+        <v>14.17730481055215</v>
       </c>
       <c r="D19" t="n">
-        <v>8.920210043011606</v>
+        <v>8.717239280102648</v>
       </c>
       <c r="E19" t="n">
-        <v>26.44492047171931</v>
+        <v>24.74303521974998</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.003679427316052</v>
+        <v>1.809837724423783</v>
       </c>
       <c r="C20" t="n">
-        <v>15.98183449481387</v>
+        <v>14.58577374362792</v>
       </c>
       <c r="D20" t="n">
-        <v>8.94229123649297</v>
+        <v>8.736320845648583</v>
       </c>
       <c r="E20" t="n">
-        <v>26.9278051586229</v>
+        <v>25.13193231370029</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.982748020731403</v>
+        <v>1.779931533210454</v>
       </c>
       <c r="C21" t="n">
-        <v>16.47721708468845</v>
+        <v>14.97567077069403</v>
       </c>
       <c r="D21" t="n">
-        <v>8.964324779842842</v>
+        <v>8.752745845724151</v>
       </c>
       <c r="E21" t="n">
-        <v>27.4242898852627</v>
+        <v>25.50834814962864</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.445290276272423</v>
+        <v>2.40215479763393</v>
       </c>
       <c r="C3" t="n">
-        <v>7.676302650519829</v>
+        <v>7.568066357913306</v>
       </c>
       <c r="D3" t="n">
-        <v>7.843535838401297</v>
+        <v>7.798611063454961</v>
       </c>
       <c r="E3" t="n">
-        <v>17.96512876519355</v>
+        <v>17.7688322190022</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.413134251246658</v>
+        <v>2.343055239245488</v>
       </c>
       <c r="C4" t="n">
-        <v>8.075242440420171</v>
+        <v>7.823794157291928</v>
       </c>
       <c r="D4" t="n">
-        <v>7.93805488642495</v>
+        <v>7.859708657599466</v>
       </c>
       <c r="E4" t="n">
-        <v>18.42643157809178</v>
+        <v>18.02655805413688</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.381111852937855</v>
+        <v>2.276775251461467</v>
       </c>
       <c r="C5" t="n">
-        <v>8.481976758288409</v>
+        <v>8.092061473170961</v>
       </c>
       <c r="D5" t="n">
-        <v>8.029313182768718</v>
+        <v>7.911576492083355</v>
       </c>
       <c r="E5" t="n">
-        <v>18.89240179399498</v>
+        <v>18.28041321671578</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.345964089736273</v>
+        <v>2.210003180309065</v>
       </c>
       <c r="C6" t="n">
-        <v>8.893356793775554</v>
+        <v>8.347526692264378</v>
       </c>
       <c r="D6" t="n">
-        <v>8.109155896207723</v>
+        <v>7.963030850807957</v>
       </c>
       <c r="E6" t="n">
-        <v>19.34847677971955</v>
+        <v>18.5205607233814</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.30853208850806</v>
+        <v>2.136397903179756</v>
       </c>
       <c r="C7" t="n">
-        <v>9.310146309339702</v>
+        <v>8.595105491995881</v>
       </c>
       <c r="D7" t="n">
-        <v>8.18283703348756</v>
+        <v>8.005825336739035</v>
       </c>
       <c r="E7" t="n">
-        <v>19.80151543133532</v>
+        <v>18.73732873191467</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.269328368059262</v>
+        <v>2.071885570770986</v>
       </c>
       <c r="C8" t="n">
-        <v>9.722573070078763</v>
+        <v>8.837885139356176</v>
       </c>
       <c r="D8" t="n">
-        <v>8.24863784906244</v>
+        <v>8.053223933103894</v>
       </c>
       <c r="E8" t="n">
-        <v>20.24053928720046</v>
+        <v>18.96299464323106</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.234618776873122</v>
+        <v>1.999864021153648</v>
       </c>
       <c r="C9" t="n">
-        <v>10.1330253399421</v>
+        <v>9.072946411057833</v>
       </c>
       <c r="D9" t="n">
-        <v>8.309669043159994</v>
+        <v>8.086341810047326</v>
       </c>
       <c r="E9" t="n">
-        <v>20.67731315997521</v>
+        <v>19.15915224225881</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.198281367066394</v>
+        <v>1.931567747847202</v>
       </c>
       <c r="C10" t="n">
-        <v>10.54847820669292</v>
+        <v>9.307115828209778</v>
       </c>
       <c r="D10" t="n">
-        <v>8.370428001281567</v>
+        <v>8.122828888620296</v>
       </c>
       <c r="E10" t="n">
-        <v>21.11718757504088</v>
+        <v>19.36151246467728</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.15652167054319</v>
+        <v>1.862719846161513</v>
       </c>
       <c r="C11" t="n">
-        <v>10.96205453526991</v>
+        <v>9.540743738418506</v>
       </c>
       <c r="D11" t="n">
-        <v>8.427303803920244</v>
+        <v>8.148006971542706</v>
       </c>
       <c r="E11" t="n">
-        <v>21.54588000973335</v>
+        <v>19.55147055612272</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.121316005823477</v>
+        <v>1.791962865108763</v>
       </c>
       <c r="C12" t="n">
-        <v>11.37894032098361</v>
+        <v>9.765831050022998</v>
       </c>
       <c r="D12" t="n">
-        <v>8.47514812551451</v>
+        <v>8.172931146509947</v>
       </c>
       <c r="E12" t="n">
-        <v>21.97540445232159</v>
+        <v>19.73072506164171</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.08419367590241</v>
+        <v>1.734603445712736</v>
       </c>
       <c r="C13" t="n">
-        <v>11.78639144008061</v>
+        <v>9.977471333722905</v>
       </c>
       <c r="D13" t="n">
-        <v>8.517997337962113</v>
+        <v>8.192153381276871</v>
       </c>
       <c r="E13" t="n">
-        <v>22.38858245394513</v>
+        <v>19.90422816071251</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.045018594862198</v>
+        <v>1.671350889969524</v>
       </c>
       <c r="C14" t="n">
-        <v>12.1948537917535</v>
+        <v>10.18823933808352</v>
       </c>
       <c r="D14" t="n">
-        <v>8.563326012630002</v>
+        <v>8.208187520562738</v>
       </c>
       <c r="E14" t="n">
-        <v>22.80319839924569</v>
+        <v>20.06777774861578</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.002275255018093</v>
+        <v>1.607625732437413</v>
       </c>
       <c r="C15" t="n">
-        <v>12.6001915291353</v>
+        <v>10.38215594950282</v>
       </c>
       <c r="D15" t="n">
-        <v>8.599880691815356</v>
+        <v>8.223950130269497</v>
       </c>
       <c r="E15" t="n">
-        <v>23.20234747596875</v>
+        <v>20.21373181220972</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.964601065294169</v>
+        <v>1.547995644043094</v>
       </c>
       <c r="C16" t="n">
-        <v>12.9961380394988</v>
+        <v>10.57681868190744</v>
       </c>
       <c r="D16" t="n">
-        <v>8.62949801615469</v>
+        <v>8.231401934906058</v>
       </c>
       <c r="E16" t="n">
-        <v>23.59023712094766</v>
+        <v>20.35621626085659</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.932325130041396</v>
+        <v>1.488995734216854</v>
       </c>
       <c r="C17" t="n">
-        <v>13.39270713381045</v>
+        <v>10.76112416691299</v>
       </c>
       <c r="D17" t="n">
-        <v>8.657841668529098</v>
+        <v>8.236777769943119</v>
       </c>
       <c r="E17" t="n">
-        <v>23.98287393238094</v>
+        <v>20.48689767107296</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.890579684098039</v>
+        <v>1.429125932094245</v>
       </c>
       <c r="C18" t="n">
-        <v>13.78387250357022</v>
+        <v>10.93903031359759</v>
       </c>
       <c r="D18" t="n">
-        <v>8.684314086764971</v>
+        <v>8.232813909283747</v>
       </c>
       <c r="E18" t="n">
-        <v>24.35876627443323</v>
+        <v>20.60097015497558</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.848491129095178</v>
+        <v>1.363025187808678</v>
       </c>
       <c r="C19" t="n">
-        <v>14.17730481055215</v>
+        <v>11.09904760028269</v>
       </c>
       <c r="D19" t="n">
-        <v>8.717239280102648</v>
+        <v>8.226541315327301</v>
       </c>
       <c r="E19" t="n">
-        <v>24.74303521974998</v>
+        <v>20.68861410341867</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.809837724423783</v>
+        <v>1.298237249643915</v>
       </c>
       <c r="C20" t="n">
-        <v>14.58577374362792</v>
+        <v>11.2535930840122</v>
       </c>
       <c r="D20" t="n">
-        <v>8.736320845648583</v>
+        <v>8.221143385141808</v>
       </c>
       <c r="E20" t="n">
-        <v>25.13193231370029</v>
+        <v>20.77297371879792</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.779931533210454</v>
+        <v>1.23549853951349</v>
       </c>
       <c r="C21" t="n">
-        <v>14.97567077069403</v>
+        <v>11.41049942147524</v>
       </c>
       <c r="D21" t="n">
-        <v>8.752745845724151</v>
+        <v>8.214569614403718</v>
       </c>
       <c r="E21" t="n">
-        <v>25.50834814962864</v>
+        <v>20.86056757539244</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.3</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.9</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.40215479763393</v>
+        <v>1.197963622199137</v>
       </c>
       <c r="C3" t="n">
-        <v>7.568066357913306</v>
+        <v>3.826668868320381</v>
       </c>
       <c r="D3" t="n">
-        <v>7.798611063454961</v>
+        <v>5.066536759553029</v>
       </c>
       <c r="E3" t="n">
-        <v>17.7688322190022</v>
+        <v>10.09116925007255</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.343055239245488</v>
+        <v>1.597851998266653</v>
       </c>
       <c r="C4" t="n">
-        <v>7.823794157291928</v>
+        <v>5.520282508860904</v>
       </c>
       <c r="D4" t="n">
-        <v>7.859708657599466</v>
+        <v>6.710744027309247</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02655805413688</v>
+        <v>13.8288785344368</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.276775251461467</v>
+        <v>2.198286583571948</v>
       </c>
       <c r="C5" t="n">
-        <v>8.092061473170961</v>
+        <v>8.196389624752971</v>
       </c>
       <c r="D5" t="n">
-        <v>7.911576492083355</v>
+        <v>8.754969404561558</v>
       </c>
       <c r="E5" t="n">
-        <v>18.28041321671578</v>
+        <v>19.14964561288648</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.210003180309065</v>
+        <v>3.005667487802501</v>
       </c>
       <c r="C6" t="n">
-        <v>8.347526692264378</v>
+        <v>12.01770247175012</v>
       </c>
       <c r="D6" t="n">
-        <v>7.963030850807957</v>
+        <v>11.74366620212395</v>
       </c>
       <c r="E6" t="n">
-        <v>18.5205607233814</v>
+        <v>26.76703616167657</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.136397903179756</v>
+        <v>3.944681251558553</v>
       </c>
       <c r="C7" t="n">
-        <v>8.595105491995881</v>
+        <v>16.41955850459578</v>
       </c>
       <c r="D7" t="n">
-        <v>8.005825336739035</v>
+        <v>14.03772693038499</v>
       </c>
       <c r="E7" t="n">
-        <v>18.73732873191467</v>
+        <v>34.40196668653932</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.071885570770986</v>
+        <v>4.753127735595672</v>
       </c>
       <c r="C8" t="n">
-        <v>8.837885139356176</v>
+        <v>20.56734011990231</v>
       </c>
       <c r="D8" t="n">
-        <v>8.053223933103894</v>
+        <v>16.42618975908794</v>
       </c>
       <c r="E8" t="n">
-        <v>18.96299464323106</v>
+        <v>41.74665761458592</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.999864021153648</v>
+        <v>5.406595824078227</v>
       </c>
       <c r="C9" t="n">
-        <v>9.072946411057833</v>
+        <v>23.60751611038305</v>
       </c>
       <c r="D9" t="n">
-        <v>8.086341810047326</v>
+        <v>18.31161608834143</v>
       </c>
       <c r="E9" t="n">
-        <v>19.15915224225881</v>
+        <v>47.32572802280271</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.931567747847202</v>
+        <v>5.842168145794043</v>
       </c>
       <c r="C10" t="n">
-        <v>9.307115828209778</v>
+        <v>25.38602636031025</v>
       </c>
       <c r="D10" t="n">
-        <v>8.122828888620296</v>
+        <v>19.46847822592652</v>
       </c>
       <c r="E10" t="n">
-        <v>19.36151246467728</v>
+        <v>50.69667273203081</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.862719846161513</v>
+        <v>6.086313019005441</v>
       </c>
       <c r="C11" t="n">
-        <v>9.540743738418506</v>
+        <v>26.47446037773296</v>
       </c>
       <c r="D11" t="n">
-        <v>8.148006971542706</v>
+        <v>20.19503158816721</v>
       </c>
       <c r="E11" t="n">
-        <v>19.55147055612272</v>
+        <v>52.75580498490561</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.791962865108763</v>
+        <v>6.216304027908651</v>
       </c>
       <c r="C12" t="n">
-        <v>9.765831050022998</v>
+        <v>26.99207202528607</v>
       </c>
       <c r="D12" t="n">
-        <v>8.172931146509947</v>
+        <v>20.54276301838349</v>
       </c>
       <c r="E12" t="n">
-        <v>19.73072506164171</v>
+        <v>53.75113907157821</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.734603445712736</v>
+        <v>6.283680458198693</v>
       </c>
       <c r="C13" t="n">
-        <v>9.977471333722905</v>
+        <v>27.25590769612801</v>
       </c>
       <c r="D13" t="n">
-        <v>8.192153381276871</v>
+        <v>21.03334894403382</v>
       </c>
       <c r="E13" t="n">
-        <v>19.90422816071251</v>
+        <v>54.57293709836053</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.671350889969524</v>
+        <v>6.227004740618837</v>
       </c>
       <c r="C14" t="n">
-        <v>10.18823933808352</v>
+        <v>27.12011909428156</v>
       </c>
       <c r="D14" t="n">
-        <v>8.208187520562738</v>
+        <v>20.91123150204848</v>
       </c>
       <c r="E14" t="n">
-        <v>20.06777774861578</v>
+        <v>54.25835533694888</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.607625732437413</v>
+        <v>6.187355417460389</v>
       </c>
       <c r="C15" t="n">
-        <v>10.38215594950282</v>
+        <v>26.97516226286285</v>
       </c>
       <c r="D15" t="n">
-        <v>8.223950130269497</v>
+        <v>20.80799250090933</v>
       </c>
       <c r="E15" t="n">
-        <v>20.21373181220972</v>
+        <v>53.97051018123257</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.547995644043094</v>
+        <v>6.264307214523237</v>
       </c>
       <c r="C16" t="n">
-        <v>10.57681868190744</v>
+        <v>27.29282502978843</v>
       </c>
       <c r="D16" t="n">
-        <v>8.231401934906058</v>
+        <v>21.18467988055279</v>
       </c>
       <c r="E16" t="n">
-        <v>20.35621626085659</v>
+        <v>54.74181212486445</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.488995734216854</v>
+        <v>6.214372457171319</v>
       </c>
       <c r="C17" t="n">
-        <v>10.76112416691299</v>
+        <v>27.14832769932555</v>
       </c>
       <c r="D17" t="n">
-        <v>8.236777769943119</v>
+        <v>21.04246565502353</v>
       </c>
       <c r="E17" t="n">
-        <v>20.48689767107296</v>
+        <v>54.4051658115204</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.429125932094245</v>
+        <v>6.16335258360602</v>
       </c>
       <c r="C18" t="n">
-        <v>10.93903031359759</v>
+        <v>26.99905466064207</v>
       </c>
       <c r="D18" t="n">
-        <v>8.232813909283747</v>
+        <v>20.97035627193604</v>
       </c>
       <c r="E18" t="n">
-        <v>20.60097015497558</v>
+        <v>54.13276351618413</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.363025187808678</v>
+        <v>6.230368191839059</v>
       </c>
       <c r="C19" t="n">
-        <v>11.09904760028269</v>
+        <v>27.2861435670139</v>
       </c>
       <c r="D19" t="n">
-        <v>8.226541315327301</v>
+        <v>21.40143404974343</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68861410341867</v>
+        <v>54.91794580859639</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.298237249643915</v>
+        <v>6.178884990120816</v>
       </c>
       <c r="C20" t="n">
-        <v>11.2535930840122</v>
+        <v>27.14088931800318</v>
       </c>
       <c r="D20" t="n">
-        <v>8.221143385141808</v>
+        <v>21.26292788017198</v>
       </c>
       <c r="E20" t="n">
-        <v>20.77297371879792</v>
+        <v>54.58270218829597</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.23549853951349</v>
+        <v>6.138694115731845</v>
       </c>
       <c r="C21" t="n">
-        <v>11.41049942147524</v>
+        <v>26.97901371788377</v>
       </c>
       <c r="D21" t="n">
-        <v>8.214569614403718</v>
+        <v>21.15479310160009</v>
       </c>
       <c r="E21" t="n">
-        <v>20.86056757539244</v>
+        <v>54.2725009352157</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.197963622199137</v>
+        <v>2.515729180323454</v>
       </c>
       <c r="C3" t="n">
-        <v>3.826668868320381</v>
+        <v>7.464689905000498</v>
       </c>
       <c r="D3" t="n">
-        <v>5.066536759553029</v>
+        <v>7.680909331192812</v>
       </c>
       <c r="E3" t="n">
-        <v>10.09116925007255</v>
+        <v>17.66132841651676</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.597851998266653</v>
+        <v>2.537464386304475</v>
       </c>
       <c r="C4" t="n">
-        <v>5.520282508860904</v>
+        <v>8.163202708381101</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710744027309247</v>
+        <v>8.434096352413924</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8288785344368</v>
+        <v>19.1347634470995</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.198286583571948</v>
+        <v>2.712274382522663</v>
       </c>
       <c r="C5" t="n">
-        <v>8.196389624752971</v>
+        <v>9.481513160597801</v>
       </c>
       <c r="D5" t="n">
-        <v>8.754969404561558</v>
+        <v>8.574761163478405</v>
       </c>
       <c r="E5" t="n">
-        <v>19.14964561288648</v>
+        <v>20.76854870659887</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.005667487802501</v>
+        <v>3.067323439763522</v>
       </c>
       <c r="C6" t="n">
-        <v>12.01770247175012</v>
+        <v>11.54993776372132</v>
       </c>
       <c r="D6" t="n">
-        <v>11.74366620212395</v>
+        <v>9.599902116252924</v>
       </c>
       <c r="E6" t="n">
-        <v>26.76703616167657</v>
+        <v>24.21716331973777</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.944681251558553</v>
+        <v>3.429470532906085</v>
       </c>
       <c r="C7" t="n">
-        <v>16.41955850459578</v>
+        <v>13.81597836223269</v>
       </c>
       <c r="D7" t="n">
-        <v>14.03772693038499</v>
+        <v>9.622050344460735</v>
       </c>
       <c r="E7" t="n">
-        <v>34.40196668653932</v>
+        <v>26.86749923959951</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.753127735595672</v>
+        <v>3.726979357201039</v>
       </c>
       <c r="C8" t="n">
-        <v>20.56734011990231</v>
+        <v>16.20049627369255</v>
       </c>
       <c r="D8" t="n">
-        <v>16.42618975908794</v>
+        <v>9.649107311189775</v>
       </c>
       <c r="E8" t="n">
-        <v>41.74665761458592</v>
+        <v>29.57658294208336</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.406595824078227</v>
+        <v>3.888359044825128</v>
       </c>
       <c r="C9" t="n">
-        <v>23.60751611038305</v>
+        <v>19.25388871353281</v>
       </c>
       <c r="D9" t="n">
-        <v>18.31161608834143</v>
+        <v>10.02760050360805</v>
       </c>
       <c r="E9" t="n">
-        <v>47.32572802280271</v>
+        <v>33.16984826196598</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.842168145794043</v>
+        <v>3.824741793589935</v>
       </c>
       <c r="C10" t="n">
-        <v>25.38602636031025</v>
+        <v>21.65433057275555</v>
       </c>
       <c r="D10" t="n">
-        <v>19.46847822592652</v>
+        <v>10.20003467038196</v>
       </c>
       <c r="E10" t="n">
-        <v>50.69667273203081</v>
+        <v>35.67910703672745</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.086313019005441</v>
+        <v>3.740802364876834</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47446037773296</v>
+        <v>23.74214469303796</v>
       </c>
       <c r="D11" t="n">
-        <v>20.19503158816721</v>
+        <v>9.953085852855718</v>
       </c>
       <c r="E11" t="n">
-        <v>52.75580498490561</v>
+        <v>37.43603291077051</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.216304027908651</v>
+        <v>3.538081281426911</v>
       </c>
       <c r="C12" t="n">
-        <v>26.99207202528607</v>
+        <v>25.49539883066711</v>
       </c>
       <c r="D12" t="n">
-        <v>20.54276301838349</v>
+        <v>9.45852062936434</v>
       </c>
       <c r="E12" t="n">
-        <v>53.75113907157821</v>
+        <v>38.49200074145836</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.283680458198693</v>
+        <v>3.28712693326734</v>
       </c>
       <c r="C13" t="n">
-        <v>27.25590769612801</v>
+        <v>27.84461309468228</v>
       </c>
       <c r="D13" t="n">
-        <v>21.03334894403382</v>
+        <v>9.276367160318388</v>
       </c>
       <c r="E13" t="n">
-        <v>54.57293709836053</v>
+        <v>40.408107188268</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.227004740618837</v>
+        <v>3.0574470578588</v>
       </c>
       <c r="C14" t="n">
-        <v>27.12011909428156</v>
+        <v>29.28585799442476</v>
       </c>
       <c r="D14" t="n">
-        <v>20.91123150204848</v>
+        <v>8.895233066575694</v>
       </c>
       <c r="E14" t="n">
-        <v>54.25835533694888</v>
+        <v>41.23853811885925</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.187355417460389</v>
+        <v>2.786062539973854</v>
       </c>
       <c r="C15" t="n">
-        <v>26.97516226286285</v>
+        <v>31.57339886765913</v>
       </c>
       <c r="D15" t="n">
-        <v>20.80799250090933</v>
+        <v>8.158077985364931</v>
       </c>
       <c r="E15" t="n">
-        <v>53.97051018123257</v>
+        <v>42.51753939299791</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.264307214523237</v>
+        <v>2.549638057837136</v>
       </c>
       <c r="C16" t="n">
-        <v>27.29282502978843</v>
+        <v>32.57561601153948</v>
       </c>
       <c r="D16" t="n">
-        <v>21.18467988055279</v>
+        <v>7.506423311717027</v>
       </c>
       <c r="E16" t="n">
-        <v>54.74181212486445</v>
+        <v>42.63167738109365</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.214372457171319</v>
+        <v>2.320429421326634</v>
       </c>
       <c r="C17" t="n">
-        <v>27.14832769932555</v>
+        <v>34.8015620338094</v>
       </c>
       <c r="D17" t="n">
-        <v>21.04246565502353</v>
+        <v>7.060228797613894</v>
       </c>
       <c r="E17" t="n">
-        <v>54.4051658115204</v>
+        <v>44.18222025274994</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.16335258360602</v>
+        <v>2.050890589125672</v>
       </c>
       <c r="C18" t="n">
-        <v>26.99905466064207</v>
+        <v>35.64108394814197</v>
       </c>
       <c r="D18" t="n">
-        <v>20.97035627193604</v>
+        <v>6.50901673158748</v>
       </c>
       <c r="E18" t="n">
-        <v>54.13276351618413</v>
+        <v>44.20099126885512</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.230368191839059</v>
+        <v>1.81460355166755</v>
       </c>
       <c r="C19" t="n">
-        <v>27.2861435670139</v>
+        <v>37.3035460580824</v>
       </c>
       <c r="D19" t="n">
-        <v>21.40143404974343</v>
+        <v>5.948281712829872</v>
       </c>
       <c r="E19" t="n">
-        <v>54.91794580859639</v>
+        <v>45.06643132257983</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.178884990120816</v>
+        <v>1.597529316781537</v>
       </c>
       <c r="C20" t="n">
-        <v>27.14088931800318</v>
+        <v>37.63324638959961</v>
       </c>
       <c r="D20" t="n">
-        <v>21.26292788017198</v>
+        <v>5.500162973226415</v>
       </c>
       <c r="E20" t="n">
-        <v>54.58270218829597</v>
+        <v>44.73093867960757</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6.138694115731845</v>
+        <v>1.394543161451467</v>
       </c>
       <c r="C21" t="n">
-        <v>26.97901371788377</v>
+        <v>38.05102912514183</v>
       </c>
       <c r="D21" t="n">
-        <v>21.15479310160009</v>
+        <v>5.160802244299419</v>
       </c>
       <c r="E21" t="n">
-        <v>54.2725009352157</v>
+        <v>44.60637453089272</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>18.3</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.232194825245222</v>
+        <v>2.126694772508088</v>
       </c>
       <c r="C3" t="n">
-        <v>22.40222597385078</v>
+        <v>2.254190903721101</v>
       </c>
       <c r="D3" t="n">
-        <v>7.033112926022599</v>
+        <v>18.90973705580909</v>
       </c>
       <c r="E3" t="n">
-        <v>34.6675337251186</v>
+        <v>23.29062273203828</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.667081323833699</v>
+        <v>2.428068164870412</v>
       </c>
       <c r="C4" t="n">
-        <v>22.95436088271918</v>
+        <v>2.42216793591773</v>
       </c>
       <c r="D4" t="n">
-        <v>8.459003291670662</v>
+        <v>19.92358790998477</v>
       </c>
       <c r="E4" t="n">
-        <v>36.08044549822354</v>
+        <v>24.77382401077291</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.326787934587671</v>
+        <v>2.969395903141547</v>
       </c>
       <c r="C5" t="n">
-        <v>23.67946010212179</v>
+        <v>2.598489823600458</v>
       </c>
       <c r="D5" t="n">
-        <v>7.974991855999942</v>
+        <v>20.50193548255657</v>
       </c>
       <c r="E5" t="n">
-        <v>35.9812398927094</v>
+        <v>26.06982120929857</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.237105281804725</v>
+        <v>3.676990280987606</v>
       </c>
       <c r="C6" t="n">
-        <v>24.348059741145</v>
+        <v>2.776873381462103</v>
       </c>
       <c r="D6" t="n">
-        <v>8.751181225931557</v>
+        <v>21.56271387699524</v>
       </c>
       <c r="E6" t="n">
-        <v>37.33634624888128</v>
+        <v>28.01657753944495</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.984589954795402</v>
+        <v>4.673722670921387</v>
       </c>
       <c r="C7" t="n">
-        <v>23.27286929040797</v>
+        <v>2.942003345316416</v>
       </c>
       <c r="D7" t="n">
-        <v>7.97091760302732</v>
+        <v>22.08696715106304</v>
       </c>
       <c r="E7" t="n">
-        <v>35.2283768482307</v>
+        <v>29.70269316730085</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.606774168293059</v>
+        <v>5.92312132680729</v>
       </c>
       <c r="C8" t="n">
-        <v>22.14214137204171</v>
+        <v>3.089658200035136</v>
       </c>
       <c r="D8" t="n">
-        <v>7.407443508174864</v>
+        <v>22.61171129898296</v>
       </c>
       <c r="E8" t="n">
-        <v>33.15635904850963</v>
+        <v>31.62449082582538</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.178987423644555</v>
+        <v>7.476610401598395</v>
       </c>
       <c r="C9" t="n">
-        <v>23.37180982404197</v>
+        <v>3.24094552125957</v>
       </c>
       <c r="D9" t="n">
-        <v>7.682273960501715</v>
+        <v>23.20252706739869</v>
       </c>
       <c r="E9" t="n">
-        <v>34.23307120818824</v>
+        <v>33.92008299025666</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.667379060007458</v>
+        <v>9.208428703582348</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92253422807874</v>
+        <v>3.362093187963627</v>
       </c>
       <c r="D10" t="n">
-        <v>7.930391057796013</v>
+        <v>23.77213708540269</v>
       </c>
       <c r="E10" t="n">
-        <v>32.52030434588221</v>
+        <v>36.34265897694866</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.456578192951581</v>
+        <v>11.13393902656324</v>
       </c>
       <c r="C11" t="n">
-        <v>20.64685126118044</v>
+        <v>3.458991686372787</v>
       </c>
       <c r="D11" t="n">
-        <v>7.660626423623074</v>
+        <v>24.12065752041031</v>
       </c>
       <c r="E11" t="n">
-        <v>30.7640558777551</v>
+        <v>38.71358823334634</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.092555961693907</v>
+        <v>13.20323035010408</v>
       </c>
       <c r="C12" t="n">
-        <v>19.42057965623687</v>
+        <v>3.541360318759094</v>
       </c>
       <c r="D12" t="n">
-        <v>7.10907074590017</v>
+        <v>24.34459417174901</v>
       </c>
       <c r="E12" t="n">
-        <v>28.62220636383094</v>
+        <v>41.08918484061218</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.741777506966521</v>
+        <v>15.45418148640117</v>
       </c>
       <c r="C13" t="n">
-        <v>20.00878397575931</v>
+        <v>3.629521262600458</v>
       </c>
       <c r="D13" t="n">
-        <v>7.351670421096602</v>
+        <v>24.73660603005476</v>
       </c>
       <c r="E13" t="n">
-        <v>29.10223190382243</v>
+        <v>43.82030877905639</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.544613115522634</v>
+        <v>17.70316912728976</v>
       </c>
       <c r="C14" t="n">
-        <v>18.83163902593625</v>
+        <v>3.718958478457342</v>
       </c>
       <c r="D14" t="n">
-        <v>7.254182874064894</v>
+        <v>24.77332339419359</v>
       </c>
       <c r="E14" t="n">
-        <v>27.63043501552378</v>
+        <v>46.19545099994069</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.297713385381604</v>
+        <v>19.88647784676424</v>
       </c>
       <c r="C15" t="n">
-        <v>20.05310988460605</v>
+        <v>3.760682755887832</v>
       </c>
       <c r="D15" t="n">
-        <v>6.53324626492829</v>
+        <v>24.57118154188917</v>
       </c>
       <c r="E15" t="n">
-        <v>27.88406953491595</v>
+        <v>48.21834214454124</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.12200018127551</v>
+        <v>22.01255067508114</v>
       </c>
       <c r="C16" t="n">
-        <v>18.32037427399564</v>
+        <v>3.80594132505361</v>
       </c>
       <c r="D16" t="n">
-        <v>5.936294573361018</v>
+        <v>24.39868847025301</v>
       </c>
       <c r="E16" t="n">
-        <v>25.37866902863216</v>
+        <v>50.21718047038775</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9315803965597983</v>
+        <v>24.02061742934756</v>
       </c>
       <c r="C17" t="n">
-        <v>19.4603011683507</v>
+        <v>3.826950725924493</v>
       </c>
       <c r="D17" t="n">
-        <v>5.755181756881568</v>
+        <v>24.35500069741402</v>
       </c>
       <c r="E17" t="n">
-        <v>26.14706332179206</v>
+        <v>52.20256885268608</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7207893469809656</v>
+        <v>25.87032827891897</v>
       </c>
       <c r="C18" t="n">
-        <v>18.20535271296608</v>
+        <v>3.820962064928587</v>
       </c>
       <c r="D18" t="n">
-        <v>5.337791720421036</v>
+        <v>24.17956238266512</v>
       </c>
       <c r="E18" t="n">
-        <v>24.26393378036808</v>
+        <v>53.87085272651267</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5413062316905639</v>
+        <v>27.5076871000618</v>
       </c>
       <c r="C19" t="n">
-        <v>18.60302925552534</v>
+        <v>3.825379929597697</v>
       </c>
       <c r="D19" t="n">
-        <v>4.780610628352801</v>
+        <v>23.85087325128329</v>
       </c>
       <c r="E19" t="n">
-        <v>23.9249461155687</v>
+        <v>55.18394028094279</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3795731148929443</v>
+        <v>28.99100970640831</v>
       </c>
       <c r="C20" t="n">
-        <v>16.68633376009317</v>
+        <v>3.810850063574844</v>
       </c>
       <c r="D20" t="n">
-        <v>4.468846827392183</v>
+        <v>23.45581797509437</v>
       </c>
       <c r="E20" t="n">
-        <v>21.5347537023783</v>
+        <v>56.25767774507753</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,33 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2435421529925063</v>
+        <v>30.29467248287766</v>
       </c>
       <c r="C21" t="n">
-        <v>15.09664860746856</v>
+        <v>3.776488893926206</v>
       </c>
       <c r="D21" t="n">
-        <v>4.364850293081318</v>
+        <v>23.13243028131547</v>
       </c>
       <c r="E21" t="n">
-        <v>19.70504105354238</v>
+        <v>57.20359165811934</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>31.49004848756856</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.760290056806133</v>
+      </c>
+      <c r="D22" t="n">
+        <v>22.9002469492611</v>
+      </c>
+      <c r="E22" t="n">
+        <v>58.1505854936358</v>
       </c>
     </row>
   </sheetData>
